--- a/mentor data/alae 4-talaria-adapted.xlsx
+++ b/mentor data/alae 4-talaria-adapted.xlsx
@@ -1304,7 +1304,7 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 44689, "mentorFile": "alae 4.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/auRHHT23/", "exitScreenshotUrl": "https://www.tradingview.com/x/h8O8qILx/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 44689, "mentorFile": "alae 4.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/auRHHT23/", "exitScreenshotUrl": "https://www.tradingview.com/x/h8O8qILx/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.02966, "sourceLowPrice": 1.02238}</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>949177</v>
+        <v>36</v>
       </c>
       <c r="BK2" t="n">
-        <v>949177</v>
+        <v>36</v>
       </c>
       <c r="BL2" t="n">
-        <v>1782554140091</v>
+        <v>1782575758686</v>
       </c>
       <c r="BM2" t="n">
         <v>1.03046</v>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="DQ2" t="inlineStr">
         <is>
-          <t>journalAccount:949177</t>
+          <t>journalAccount:58</t>
         </is>
       </c>
       <c r="DR2" t="inlineStr">
         <is>
-          <t>journalAccount:949177</t>
+          <t>journalAccount:58</t>
         </is>
       </c>
       <c r="DS2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 44691, "mentorFile": "alae 4.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Rt33SewC/", "exitScreenshotUrl": "https://www.tradingview.com/x/rkYkcGRw/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 44691, "mentorFile": "alae 4.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Rt33SewC/", "exitScreenshotUrl": "https://www.tradingview.com/x/rkYkcGRw/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.03742, "sourceLowPrice": 1.03635}</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1877,13 +1877,13 @@
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>949177</v>
+        <v>36</v>
       </c>
       <c r="BK3" t="n">
-        <v>949177</v>
+        <v>36</v>
       </c>
       <c r="BL3" t="n">
-        <v>1782554140091</v>
+        <v>1782575758686</v>
       </c>
       <c r="BM3" t="n">
         <v>1.03768</v>
@@ -2085,12 +2085,12 @@
       </c>
       <c r="DQ3" t="inlineStr">
         <is>
-          <t>journalAccount:949177</t>
+          <t>journalAccount:58</t>
         </is>
       </c>
       <c r="DR3" t="inlineStr">
         <is>
-          <t>journalAccount:949177</t>
+          <t>journalAccount:58</t>
         </is>
       </c>
       <c r="DS3" t="inlineStr">

--- a/mentor data/alae 4-talaria-adapted.xlsx
+++ b/mentor data/alae 4-talaria-adapted.xlsx
@@ -1304,7 +1304,7 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 44689, "mentorFile": "alae 4.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/auRHHT23/", "exitScreenshotUrl": "https://www.tradingview.com/x/h8O8qILx/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.02966, "sourceLowPrice": 1.02238}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 44689, "mentorFile": "alae 4.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/auRHHT23/", "exitScreenshotUrl": "https://www.tradingview.com/x/h8O8qILx/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.02966, "sourceLowPrice": 1.02238, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -1359,7 +1359,7 @@
         <v>36</v>
       </c>
       <c r="BL2" t="n">
-        <v>1782575758686</v>
+        <v>1782579162535</v>
       </c>
       <c r="BM2" t="n">
         <v>1.03046</v>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 44691, "mentorFile": "alae 4.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Rt33SewC/", "exitScreenshotUrl": "https://www.tradingview.com/x/rkYkcGRw/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.03742, "sourceLowPrice": 1.03635}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 44691, "mentorFile": "alae 4.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Rt33SewC/", "exitScreenshotUrl": "https://www.tradingview.com/x/rkYkcGRw/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.03742, "sourceLowPrice": 1.03635, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1883,7 +1883,7 @@
         <v>36</v>
       </c>
       <c r="BL3" t="n">
-        <v>1782575758686</v>
+        <v>1782579162535</v>
       </c>
       <c r="BM3" t="n">
         <v>1.03768</v>
